--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125922611</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107278</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Prästmossen, SV om Hållnäs kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>654971</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6713082</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Litet blommande bestånd (ca. 1 m2), vid östra vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107278</v>
+        <v>107281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107281</v>
+        <v>107282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107282</v>
+        <v>107284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107284</v>
+        <v>107288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107288</v>
+        <v>107289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107289</v>
+        <v>107291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107291</v>
+        <v>107293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107293</v>
+        <v>107297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107297</v>
+        <v>107310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107310</v>
+        <v>107313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125922611</v>
       </c>
       <c r="B3" t="n">
-        <v>107313</v>
+        <v>107322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101898572</v>
+        <v>99959520</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654895.2623634561</v>
+        <v>654895</v>
       </c>
       <c r="R2" t="n">
-        <v>6712896.587394926</v>
+        <v>6712897</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>02:44</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
+          <t>2022-04-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>02:44</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125922611</v>
+        <v>101898537</v>
       </c>
       <c r="B3" t="n">
-        <v>107322</v>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220103</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,29 +827,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Prästmossen, SV om Hållnäs kyrka, Upl</t>
+          <t>Hållnäs, Upl 3328 m SW, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654971</v>
+        <v>654973</v>
       </c>
       <c r="R3" t="n">
-        <v>6713082</v>
+        <v>6713097</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,17 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>02:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Litet blommande bestånd (ca. 1 m2), vid östra vägkanten.</t>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>02:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,24 +897,940 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägkant.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101898504</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tierp 3396 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>654895</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6712897</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101898572</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tierp 3396 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>654895</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6712897</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87281804</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Valnässkogen, avtagsväg, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>654917</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6712819</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Någon blommar, flera i frukt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsvägskant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127475159</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ängvreta, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>654922</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6712989</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125922610</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Prästmossen, SV om Hållnäs kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>654867</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6712840</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Litet blommande bestånd, vid västra vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Vägkant.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125922611</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Prästmossen, SV om Hållnäs kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>654971</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6713082</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Litet blommande bestånd (ca. 1 m2), vid östra vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Vägkant.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127475158</v>
+      </c>
+      <c r="B10" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ängvreta, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>654971</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6713096</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127475161</v>
+      </c>
+      <c r="B11" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ängvreta, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>654870</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6712840</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48687-2023 artfynd.xlsx
+++ b/artfynd/A 48687-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99959520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101898537</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101898504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101898572</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87281804</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475159</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125922610</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1611,6 +1651,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125922611</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475158</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,8 +1881,25 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127475161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>